--- a/verification_forms/029_property_lease_verification_form--verification_forms.xlsx
+++ b/verification_forms/029_property_lease_verification_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'lease_status',_'label':_'lease_status'}</t>
+          <t>lease_status</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'lease_status', 'label': 'Lease Status'}</t>
+          <t>Lease Status</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lease_type',_'label':_'lease_type'}</t>
+          <t>lease_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'lease_type', 'label': 'Lease Type'}</t>
+          <t>Lease Type</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'lease_length',_'label':_'lease_length'}</t>
+          <t>lease_length</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'lease_length', 'label': 'Lease Length'}</t>
+          <t>Lease Length</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'lease_terms',_'label':_'lease_terms'}</t>
+          <t>lease_terms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'lease_terms', 'label': 'Lease Terms'}</t>
+          <t>Lease Terms</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'rental_history',_'label':_'rental_history'}</t>
+          <t>rental_history</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'rental_history', 'label': 'Rental History'}</t>
+          <t>Rental History</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'employment_status',_'label':_'employment_status'}</t>
+          <t>employment_status</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'employment_status', 'label': 'Employment Status'}</t>
+          <t>Employment Status</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'income_verification',_'label':_'income_verification'}</t>
+          <t>income_verification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'income_verification', 'label': 'Income Verification'}</t>
+          <t>Income Verification</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'landlord_reference',_'label':_'landlord_reference'}</t>
+          <t>landlord_reference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'landlord_reference', 'label': 'Landlord Reference'}</t>
+          <t>Landlord Reference</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'property_manager_reference',_'label':_'property_manager_reference'}</t>
+          <t>property_manager_reference</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'property_manager_reference', 'label': 'Property Manager Reference'}</t>
+          <t>Property Manager Reference</t>
         </is>
       </c>
     </row>
